--- a/data/trans_camb/IP18A03-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/IP18A03-Estudios-trans_camb.xlsx
@@ -523,7 +523,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que su última consulta al médico fue por diagnóstico y vacunación</t>
+          <t>Menores que su última consulta al médico fue por diagnóstico y tratamiento</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1,0</t>
+          <t>21,47</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-13,37</t>
+          <t>24,39</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-7,12</t>
+          <t>23,56</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-10,4; 16,46</t>
+          <t>-8,57; 17,08</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,76; 25,46</t>
+          <t>-2,96; 23,83</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-32,53; 29,25</t>
+          <t>-10,05; 41,38</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-13,56; 13,44</t>
+          <t>-14,8; 12,13</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-1,66; 23,85</t>
+          <t>-2,16; 24,44</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-43,4; 15,89</t>
+          <t>-2,69; 39,06</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-8,18; 10,43</t>
+          <t>-7,79; 10,87</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2,24; 20,43</t>
+          <t>2,46; 20,67</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-28,52; 13,86</t>
+          <t>3,61; 36,32</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>37,27%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-21,53%</t>
+          <t>39,26%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-11,88%</t>
+          <t>39,33%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-15,53; 31,53</t>
+          <t>-13,57; 34,28</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-4,62; 50,36</t>
+          <t>-4,4; 46,56</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-53,38; 55,3</t>
+          <t>-15,32; 79,23</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-19,96; 24,44</t>
+          <t>-21,32; 21,96</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-2,43; 42,98</t>
+          <t>-2,83; 45,0</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-68,82; 26,46</t>
+          <t>-1,82; 70,01</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-12,53; 18,54</t>
+          <t>-12,41; 19,82</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>3,56; 36,81</t>
+          <t>3,92; 37,56</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-45,85; 24,76</t>
+          <t>6,9; 65,3</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-28,78</t>
+          <t>9,04</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-34,22</t>
+          <t>12,56</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-31,94</t>
+          <t>11,07</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-6,95; 3,95</t>
+          <t>-6,84; 4,13</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-5,41; 5,37</t>
+          <t>-5,83; 4,79</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-39,33; -16,03</t>
+          <t>-0,39; 18,49</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-4,29; 6,65</t>
+          <t>-4,06; 6,56</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-6,84; 3,65</t>
+          <t>-6,91; 3,95</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-44,21; -24,03</t>
+          <t>3,08; 19,4</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-3,74; 3,9</t>
+          <t>-3,7; 3,96</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-4,44; 2,81</t>
+          <t>-4,4; 3,19</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-39,24; -23,69</t>
+          <t>5,04; 17,17</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-43,08%</t>
+          <t>13,53%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-51,33%</t>
+          <t>18,84%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-47,86%</t>
+          <t>16,59%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-9,95; 6,22</t>
+          <t>-9,76; 6,43</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-7,86; 8,45</t>
+          <t>-8,33; 7,54</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-58,12; -24,14</t>
+          <t>-0,57; 28,43</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-6,16; 10,31</t>
+          <t>-5,81; 10,12</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-9,93; 5,66</t>
+          <t>-10,05; 6,18</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-64,44; -35,25</t>
+          <t>4,81; 30,23</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-5,49; 6,03</t>
+          <t>-5,38; 6,12</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-6,51; 4,4</t>
+          <t>-6,47; 4,95</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-57,96; -35,57</t>
+          <t>7,52; 26,3</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>-26,02</t>
+          <t>24,06</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-33,44</t>
+          <t>18,97</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-29,75</t>
+          <t>21,56</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,05; 20,19</t>
+          <t>1,17; 20,2</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-5,5; 12,91</t>
+          <t>-6,9; 12,63</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-40,16; -9,68</t>
+          <t>8,98; 37,02</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-6,44; 12,46</t>
+          <t>-5,65; 12,29</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-7,89; 11,1</t>
+          <t>-7,72; 10,8</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-48,59; -17,55</t>
+          <t>1,75; 31,77</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,91; 13,72</t>
+          <t>0,79; 13,44</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-2,85; 9,67</t>
+          <t>-4,02; 9,34</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-39,61; -17,06</t>
+          <t>10,43; 31,05</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>-46,84%</t>
+          <t>43,32%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-56,54%</t>
+          <t>32,08%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-51,96%</t>
+          <t>37,66%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>3,21; 39,19</t>
+          <t>2,28; 41,35</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-9,23; 25,53</t>
+          <t>-11,51; 24,74</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-69,46; -18,92</t>
+          <t>15,64; 70,34</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-9,69; 22,83</t>
+          <t>-8,75; 22,76</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-11,95; 20,93</t>
+          <t>-12,25; 19,71</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-79,75; -30,98</t>
+          <t>3,25; 56,91</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1,48; 25,63</t>
+          <t>1,31; 24,96</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-4,82; 18,32</t>
+          <t>-6,66; 17,63</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-68,2; -30,93</t>
+          <t>18,26; 56,88</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-25,77</t>
+          <t>14,29</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-32,41</t>
+          <t>15,05</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-29,44</t>
+          <t>14,81</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-2,24; 6,68</t>
+          <t>-2,05; 6,82</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,03; 6,82</t>
+          <t>-2,34; 6,79</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-34,43; -16,73</t>
+          <t>6,32; 21,55</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-2,81; 5,8</t>
+          <t>-2,63; 5,61</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-3,82; 4,72</t>
+          <t>-3,76; 4,77</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-40,37; -24,39</t>
+          <t>8,23; 21,73</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-1,23; 5,17</t>
+          <t>-1,06; 4,84</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-1,62; 4,72</t>
+          <t>-1,69; 4,22</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-35,24; -22,93</t>
+          <t>9,74; 19,77</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>-41,03%</t>
+          <t>22,75%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-50,29%</t>
+          <t>23,36%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-46,26%</t>
+          <t>23,28%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-3,44; 10,87</t>
+          <t>-3,25; 11,21</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-3,09; 11,3</t>
+          <t>-3,4; 11,38</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-53,83; -27,21</t>
+          <t>9,46; 34,97</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-4,22; 9,35</t>
+          <t>-3,93; 8,91</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-5,74; 7,53</t>
+          <t>-5,73; 7,6</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-61,76; -38,56</t>
+          <t>12,75; 35,24</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-1,88; 8,31</t>
+          <t>-1,61; 7,83</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-2,49; 7,61</t>
+          <t>-2,64; 6,69</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-55,28; -36,54</t>
+          <t>15,15; 31,4</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP18A03-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/IP18A03-Estudios-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-8,57; 17,08</t>
+          <t>-8,42; 17,51</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,96; 23,83</t>
+          <t>-2,12; 24,92</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-10,05; 41,38</t>
+          <t>-10,44; 42,32</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-14,8; 12,13</t>
+          <t>-14,11; 10,63</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-2,16; 24,44</t>
+          <t>-3,25; 22,65</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-2,69; 39,06</t>
+          <t>-7,19; 38,89</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-7,79; 10,87</t>
+          <t>-8,18; 10,57</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2,46; 20,67</t>
+          <t>1,71; 20,4</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>3,61; 36,32</t>
+          <t>5,28; 36,84</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-13,57; 34,28</t>
+          <t>-12,87; 34,22</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-4,4; 46,56</t>
+          <t>-3,13; 50,99</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-15,32; 79,23</t>
+          <t>-18,55; 79,65</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-21,32; 21,96</t>
+          <t>-21,2; 19,29</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-2,83; 45,0</t>
+          <t>-4,57; 40,54</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-1,82; 70,01</t>
+          <t>-5,7; 68,44</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-12,41; 19,82</t>
+          <t>-13,09; 19,41</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>3,92; 37,56</t>
+          <t>2,73; 37,8</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>6,9; 65,3</t>
+          <t>9,18; 66,28</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-6,84; 4,13</t>
+          <t>-6,35; 4,25</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-5,83; 4,79</t>
+          <t>-5,63; 5,6</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,39; 18,49</t>
+          <t>-0,99; 17,86</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-4,06; 6,56</t>
+          <t>-3,92; 6,33</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-6,91; 3,95</t>
+          <t>-6,74; 4,07</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,08; 19,4</t>
+          <t>4,59; 19,85</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-3,7; 3,96</t>
+          <t>-3,77; 3,7</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-4,4; 3,19</t>
+          <t>-4,17; 3,11</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>5,04; 17,17</t>
+          <t>4,73; 17,07</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-9,76; 6,43</t>
+          <t>-9,31; 6,6</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-8,33; 7,54</t>
+          <t>-8,15; 8,84</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-0,57; 28,43</t>
+          <t>-1,24; 27,71</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-5,81; 10,12</t>
+          <t>-5,71; 9,99</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-10,05; 6,18</t>
+          <t>-9,85; 6,32</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,81; 30,23</t>
+          <t>6,7; 30,77</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-5,38; 6,12</t>
+          <t>-5,51; 5,71</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-6,47; 4,95</t>
+          <t>-6,07; 4,8</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>7,52; 26,3</t>
+          <t>6,93; 25,96</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,17; 20,2</t>
+          <t>1,71; 20,32</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-6,9; 12,63</t>
+          <t>-5,08; 13,87</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8,98; 37,02</t>
+          <t>10,36; 36,26</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-5,65; 12,29</t>
+          <t>-5,56; 12,31</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-7,72; 10,8</t>
+          <t>-7,14; 11,15</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,75; 31,77</t>
+          <t>2,65; 30,85</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,79; 13,44</t>
+          <t>0,77; 13,33</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-4,02; 9,34</t>
+          <t>-4,01; 8,74</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>10,43; 31,05</t>
+          <t>9,95; 31,13</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2,28; 41,35</t>
+          <t>2,87; 39,87</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-11,51; 24,74</t>
+          <t>-8,68; 28,25</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>15,64; 70,34</t>
+          <t>18,35; 70,66</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-8,75; 22,76</t>
+          <t>-8,85; 22,96</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-12,25; 19,71</t>
+          <t>-11,28; 21,15</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>3,25; 56,91</t>
+          <t>4,81; 56,26</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1,31; 24,96</t>
+          <t>1,3; 24,93</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-6,66; 17,63</t>
+          <t>-6,69; 16,23</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>18,26; 56,88</t>
+          <t>16,51; 57,82</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-2,05; 6,82</t>
+          <t>-2,13; 6,94</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,34; 6,79</t>
+          <t>-1,84; 6,97</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>6,32; 21,55</t>
+          <t>5,84; 21,44</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-2,63; 5,61</t>
+          <t>-2,85; 5,68</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-3,76; 4,77</t>
+          <t>-3,45; 4,7</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>8,23; 21,73</t>
+          <t>8,94; 21,16</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-1,06; 4,84</t>
+          <t>-1,12; 4,82</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-1,69; 4,22</t>
+          <t>-1,66; 4,42</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>9,74; 19,77</t>
+          <t>9,66; 20,03</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-3,25; 11,21</t>
+          <t>-3,29; 11,35</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-3,4; 11,38</t>
+          <t>-2,84; 11,62</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>9,46; 34,97</t>
+          <t>9,32; 35,39</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-3,93; 8,91</t>
+          <t>-4,31; 9,17</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-5,73; 7,6</t>
+          <t>-5,21; 7,57</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>12,75; 35,24</t>
+          <t>13,58; 33,26</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-1,61; 7,83</t>
+          <t>-1,71; 7,74</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-2,64; 6,69</t>
+          <t>-2,56; 7,12</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>15,15; 31,4</t>
+          <t>15,09; 32,13</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP18A03-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/IP18A03-Estudios-trans_camb.xlsx
@@ -523,20 +523,20 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que su última consulta al médico fue por diagnóstico y tratamiento</t>
+          <t>Menores cuya última consulta médica fue por diagnóstico y tratamiento</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,32 +624,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>-1,36</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>11,42</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>24,81</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>4,48</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>11,25</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>21,47</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>-1,36</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>11,42</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>24,39</t>
+          <t>22,36</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>23,56</t>
+          <t>24,27</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-8,42; 17,51</t>
+          <t>-13,56; 13,44</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,12; 24,92</t>
+          <t>-1,66; 23,85</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-10,44; 42,32</t>
+          <t>-1,88; 39,62</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-14,11; 10,63</t>
+          <t>-10,4; 16,46</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-3,25; 22,65</t>
+          <t>-2,76; 25,46</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-7,19; 38,89</t>
+          <t>-11,26; 39,42</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-8,18; 10,57</t>
+          <t>-8,18; 10,43</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,71; 20,4</t>
+          <t>2,24; 20,43</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>5,28; 36,84</t>
+          <t>4,04; 36,1</t>
         </is>
       </c>
     </row>
@@ -730,32 +730,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>-2,19%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>18,38%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>39,94%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>7,78%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>19,53%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>37,27%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-2,19%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>18,38%</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>39,26%</t>
+          <t>38,82%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>39,33%</t>
+          <t>40,52%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-12,87; 34,22</t>
+          <t>-19,96; 24,44</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-3,13; 50,99</t>
+          <t>-2,43; 42,98</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-18,55; 79,65</t>
+          <t>-0,81; 71,8</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-21,2; 19,29</t>
+          <t>-15,53; 31,53</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-4,57; 40,54</t>
+          <t>-4,62; 50,36</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-5,7; 68,44</t>
+          <t>-17,86; 74,87</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-13,09; 19,41</t>
+          <t>-12,53; 18,54</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2,73; 37,8</t>
+          <t>3,56; 36,81</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>9,18; 66,28</t>
+          <t>9,67; 64,64</t>
         </is>
       </c>
     </row>
@@ -840,32 +840,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>1,21</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
           <t>-1,41</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>12,57</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>-1,41</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>-0,22</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>9,04</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>1,21</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-1,41</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>12,56</t>
+          <t>7,33</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>11,07</t>
+          <t>10,31</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-6,35; 4,25</t>
+          <t>-4,29; 6,65</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-5,63; 5,6</t>
+          <t>-6,84; 3,65</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,99; 17,86</t>
+          <t>4,11; 20,76</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-3,92; 6,33</t>
+          <t>-6,95; 3,95</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-6,74; 4,07</t>
+          <t>-5,41; 5,37</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,59; 19,85</t>
+          <t>-3,36; 16,74</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-3,77; 3,7</t>
+          <t>-3,74; 3,9</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-4,17; 3,11</t>
+          <t>-4,44; 2,81</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4,73; 17,07</t>
+          <t>3,51; 16,24</t>
         </is>
       </c>
     </row>
@@ -946,32 +946,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>1,81%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>-2,11%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>18,86%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>-2,11%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>-0,34%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>13,53%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>1,81%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-2,11%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>18,84%</t>
+          <t>10,97%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>16,59%</t>
+          <t>15,45%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-9,31; 6,6</t>
+          <t>-6,16; 10,31</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-8,15; 8,84</t>
+          <t>-9,93; 5,66</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-1,24; 27,71</t>
+          <t>5,84; 32,08</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-5,71; 9,99</t>
+          <t>-9,95; 6,22</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-9,85; 6,32</t>
+          <t>-7,86; 8,45</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>6,7; 30,77</t>
+          <t>-4,84; 25,6</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-5,51; 5,71</t>
+          <t>-5,49; 6,03</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-6,07; 4,8</t>
+          <t>-6,51; 4,4</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>6,93; 25,96</t>
+          <t>5,28; 24,92</t>
         </is>
       </c>
     </row>
@@ -1056,32 +1056,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>3,48</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>1,65</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>17,66</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>10,91</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>3,82</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>24,06</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>3,48</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>1,65</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>18,97</t>
+          <t>22,4</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>21,56</t>
+          <t>20,09</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,71; 20,32</t>
+          <t>-6,44; 12,46</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-5,08; 13,87</t>
+          <t>-7,89; 11,1</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>10,36; 36,26</t>
+          <t>0,04; 32,31</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-5,56; 12,31</t>
+          <t>2,05; 20,19</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-7,14; 11,15</t>
+          <t>-5,5; 12,91</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,65; 30,85</t>
+          <t>6,14; 36,61</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,77; 13,33</t>
+          <t>0,91; 13,72</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-4,01; 8,74</t>
+          <t>-2,85; 9,67</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>9,95; 31,13</t>
+          <t>9,06; 29,45</t>
         </is>
       </c>
     </row>
@@ -1162,32 +1162,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>5,88%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>2,79%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>29,86%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>19,64%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>6,89%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>43,32%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>5,88%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>2,79%</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>32,08%</t>
+          <t>40,32%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>37,66%</t>
+          <t>35,09%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2,87; 39,87</t>
+          <t>-9,69; 22,83</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-8,68; 28,25</t>
+          <t>-11,95; 20,93</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>18,35; 70,66</t>
+          <t>0,84; 59,88</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-8,85; 22,96</t>
+          <t>3,21; 39,19</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-11,28; 21,15</t>
+          <t>-9,23; 25,53</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>4,81; 56,26</t>
+          <t>12,52; 72,14</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1,3; 24,93</t>
+          <t>1,48; 25,63</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-6,69; 16,23</t>
+          <t>-4,82; 18,32</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>16,51; 57,82</t>
+          <t>15,63; 54,79</t>
         </is>
       </c>
     </row>
@@ -1272,32 +1272,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>1,45</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>0,46</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>14,8</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>2,41</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>2,26</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>14,29</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>1,45</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>0,46</t>
-        </is>
-      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>15,05</t>
+          <t>12,75</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>14,81</t>
+          <t>13,98</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-2,13; 6,94</t>
+          <t>-2,81; 5,8</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,84; 6,97</t>
+          <t>-3,82; 4,72</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>5,84; 21,44</t>
+          <t>7,52; 20,59</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-2,85; 5,68</t>
+          <t>-2,24; 6,68</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-3,45; 4,7</t>
+          <t>-2,03; 6,82</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>8,94; 21,16</t>
+          <t>3,9; 20,14</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-1,12; 4,82</t>
+          <t>-1,23; 5,17</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-1,66; 4,42</t>
+          <t>-1,62; 4,72</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>9,66; 20,03</t>
+          <t>8,78; 19,1</t>
         </is>
       </c>
     </row>
@@ -1378,32 +1378,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>2,26%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>0,71%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>22,97%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>3,84%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>3,6%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>22,75%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>2,26%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>0,71%</t>
-        </is>
-      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>23,36%</t>
+          <t>20,3%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>23,28%</t>
+          <t>21,97%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-3,29; 11,35</t>
+          <t>-4,22; 9,35</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-2,84; 11,62</t>
+          <t>-5,74; 7,53</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>9,32; 35,39</t>
+          <t>11,59; 33,41</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-4,31; 9,17</t>
+          <t>-3,44; 10,87</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-5,21; 7,57</t>
+          <t>-3,09; 11,3</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>13,58; 33,26</t>
+          <t>6,21; 33,29</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-1,71; 7,74</t>
+          <t>-1,88; 8,31</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-2,56; 7,12</t>
+          <t>-2,49; 7,61</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>15,09; 32,13</t>
+          <t>13,87; 30,44</t>
         </is>
       </c>
     </row>
